--- a/30_table/01_테스트버전/Table_Data_Character.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Character.xlsx
@@ -5240,19 +5240,19 @@
         <v>3</v>
       </c>
       <c r="L4" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P4" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="33"/>
@@ -5307,19 +5307,19 @@
         <v>3</v>
       </c>
       <c r="L5" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P5" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="33"/>
       <c r="R5" s="33"/>
@@ -5373,19 +5373,19 @@
         <v>3</v>
       </c>
       <c r="L6" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="33"/>
       <c r="R6" s="33"/>
@@ -5439,19 +5439,19 @@
         <v>3</v>
       </c>
       <c r="L7" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="33"/>
       <c r="R7" s="33"/>
@@ -5505,19 +5505,19 @@
         <v>3</v>
       </c>
       <c r="L8" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="33"/>
       <c r="R8" s="33"/>
@@ -5571,19 +5571,19 @@
         <v>6</v>
       </c>
       <c r="L9" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="33" t="s">
         <v>149</v>
@@ -5650,19 +5650,19 @@
         <v>6</v>
       </c>
       <c r="L10" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="33" t="s">
         <v>149</v>
@@ -5729,19 +5729,19 @@
         <v>6</v>
       </c>
       <c r="L11" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="33" t="s">
         <v>149</v>
@@ -5808,19 +5808,19 @@
         <v>6</v>
       </c>
       <c r="L12" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P12" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="33" t="s">
         <v>149</v>
@@ -5887,19 +5887,19 @@
         <v>6</v>
       </c>
       <c r="L13" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P13" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="33" t="s">
         <v>149</v>
@@ -6914,19 +6914,19 @@
         <v>15</v>
       </c>
       <c r="L26" s="36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M26" s="36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" s="36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" s="36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P26" s="36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="33" t="s">
         <v>252</v>
